--- a/nr-doc-core-procedure/ig/StructureDefinition-fr-core-procedure-priority-extension.xlsx
+++ b/nr-doc-core-procedure/ig/StructureDefinition-fr-core-procedure-priority-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T08:32:23+00:00</t>
+    <t>2026-09-16T15:06:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -347,7 +347,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActPriority-cisis|20260619134042</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActPriority-cisis|20260716085852</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}

--- a/nr-doc-core-procedure/ig/StructureDefinition-fr-core-procedure-priority-extension.xlsx
+++ b/nr-doc-core-procedure/ig/StructureDefinition-fr-core-procedure-priority-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T15:06:55+00:00</t>
+    <t>2026-09-16T15:10:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-procedure/ig/StructureDefinition-fr-core-procedure-priority-extension.xlsx
+++ b/nr-doc-core-procedure/ig/StructureDefinition-fr-core-procedure-priority-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T15:10:32+00:00</t>
+    <t>2026-09-16T15:30:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-procedure/ig/StructureDefinition-fr-core-procedure-priority-extension.xlsx
+++ b/nr-doc-core-procedure/ig/StructureDefinition-fr-core-procedure-priority-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T15:30:48+00:00</t>
+    <t>2026-09-17T13:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
